--- a/outputs/Block2_TimeMachine_Scorecard_v12.xlsx
+++ b/outputs/Block2_TimeMachine_Scorecard_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>Test Election</t>
   </si>
@@ -76,7 +76,10 @@
     <t>ExpectedVoteAnchor</t>
   </si>
   <si>
-    <t>Ridge</t>
+    <t>Derived downstream from 435 races</t>
+  </si>
+  <si>
+    <t>Derived downstream from Senate races</t>
   </si>
 </sst>
 </file>
@@ -497,24 +500,6 @@
       <c r="E2">
         <v>4.058252427184449</v>
       </c>
-      <c r="F2">
-        <v>226</v>
-      </c>
-      <c r="G2">
-        <v>233</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
-        <v>43</v>
-      </c>
-      <c r="J2">
-        <v>51</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
       <c r="L2" t="s">
         <v>19</v>
       </c>
@@ -522,7 +507,7 @@
         <v>20</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -541,24 +526,6 @@
       <c r="E3">
         <v>3.131304347826081</v>
       </c>
-      <c r="F3">
-        <v>229</v>
-      </c>
-      <c r="G3">
-        <v>193</v>
-      </c>
-      <c r="H3">
-        <v>36</v>
-      </c>
-      <c r="I3">
-        <v>53</v>
-      </c>
-      <c r="J3">
-        <v>53</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
       <c r="L3" t="s">
         <v>19</v>
       </c>
@@ -566,7 +533,7 @@
         <v>20</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -585,24 +552,6 @@
       <c r="E4">
         <v>3.073648648648641</v>
       </c>
-      <c r="F4">
-        <v>173</v>
-      </c>
-      <c r="G4">
-        <v>188</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
-      <c r="I4">
-        <v>50</v>
-      </c>
-      <c r="J4">
-        <v>46</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
       <c r="L4" t="s">
         <v>19</v>
       </c>
@@ -610,7 +559,7 @@
         <v>20</v>
       </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -629,24 +578,6 @@
       <c r="E5">
         <v>0.9274701411509145</v>
       </c>
-      <c r="F5">
-        <v>202</v>
-      </c>
-      <c r="G5">
-        <v>235</v>
-      </c>
-      <c r="H5">
-        <v>33</v>
-      </c>
-      <c r="I5">
-        <v>47</v>
-      </c>
-      <c r="J5">
-        <v>47</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
       <c r="L5" t="s">
         <v>19</v>
       </c>
@@ -654,7 +585,7 @@
         <v>20</v>
       </c>
       <c r="N5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -673,24 +604,6 @@
       <c r="E6">
         <v>0.1057486631016071</v>
       </c>
-      <c r="F6">
-        <v>215</v>
-      </c>
-      <c r="G6">
-        <v>213</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>49</v>
-      </c>
-      <c r="J6">
-        <v>51</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
       <c r="L6" t="s">
         <v>19</v>
       </c>
@@ -698,7 +611,7 @@
         <v>20</v>
       </c>
       <c r="N6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
